--- a/Excel/22_VLookUp/Pinterest_VLOOKUP_Practice.xlsx
+++ b/Excel/22_VLookUp/Pinterest_VLOOKUP_Practice.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Pinterest-Analytics-Project\Excel\22_VLookUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A534B50E-3212-470D-BC59-25830AA10117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6370845A-97C3-4E32-AFE8-BD1F325CE6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{568823AC-CE67-4111-AF51-A0867C8A22E4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{568823AC-CE67-4111-AF51-A0867C8A22E4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Pin_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Lookup_Practice" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,9 +36,83 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
+  <si>
+    <t>Pin Name</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Impressions</t>
+  </si>
+  <si>
+    <t>Engagement</t>
+  </si>
+  <si>
+    <t>Wooden Knife Holder</t>
+  </si>
+  <si>
+    <t>Kitchen</t>
+  </si>
+  <si>
+    <t>Leak-Proof Tiffin Box</t>
+  </si>
+  <si>
+    <t>Home Decor Ideas</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Womens Fashion</t>
+  </si>
+  <si>
+    <t>Fashion</t>
+  </si>
+  <si>
+    <t>Beauty Self-Care</t>
+  </si>
+  <si>
+    <t>Beauty</t>
+  </si>
+  <si>
+    <t>Kitchen Storage</t>
+  </si>
+  <si>
+    <t>Handbag Fashion</t>
+  </si>
+  <si>
+    <t>Home Essentials</t>
+  </si>
+  <si>
+    <t>Skincare Products</t>
+  </si>
+  <si>
+    <t>Desk Setup</t>
+  </si>
+  <si>
+    <t>Pinterest Pin Lookup</t>
+  </si>
+  <si>
+    <t>Enter Pin Name</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>IFERROR ----- Formula</t>
+  </si>
+  <si>
+    <t>Premium Lunch Box</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -45,16 +120,68 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -62,17 +189,382 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -83,6 +575,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D10027B-EBF9-4044-AFDA-836536F03CB8}" name="Table1" displayName="Table1" ref="A1:D11" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:D11" xr:uid="{1D10027B-EBF9-4044-AFDA-836536F03CB8}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{BDB77BA6-4E7D-4021-A6C9-81D8EB8217AF}" name="Pin Name" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{C45A7E32-A34F-46D7-956E-5A8E9E74C3FB}" name="Category" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{CB2CFB01-0B84-4D80-B3F4-D04ADD9CCB0E}" name="Impressions" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{57A78DB7-E306-403C-AE39-415DDA1E983F}" name="Engagement" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +907,285 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0E42A7E-156A-4D44-A58F-297494FB9D18}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="4" width="17.6328125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>214</v>
+      </c>
+      <c r="D2" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>93</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>41</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2">
+        <v>38</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2">
+        <v>57</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>76</v>
+      </c>
+      <c r="D7" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2">
+        <v>45</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2">
+        <v>31</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2">
+        <v>29</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9">
+        <v>23</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D861D977-7049-4845-B603-F480AB125E46}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="24.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="13"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="11" t="str">
+        <f>VLOOKUP(B3,Table1[#All],2,FALSE)</f>
+        <v>Kitchen</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="11">
+        <f>VLOOKUP(B3,Table1[#All],3,FALSE)</f>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="11">
+        <f>VLOOKUP(B3,Table1[#All],4,FALSE)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="17"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="11" t="str">
+        <f>IFERROR(VLOOKUP(B13,Table1[#All],2,FALSE),"Not Found")</f>
+        <v>Not Found</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="11" t="str">
+        <f>IFERROR(VLOOKUP(B13,Table1[#All],3,FALSE),"Not Found")</f>
+        <v>Not Found</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="11" t="str">
+        <f>IFERROR(VLOOKUP(B13,Table1[#All],4,FALSE),"not found")</f>
+        <v>not found</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A10:B10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>